--- a/site/exports/jlu-math.xlsx
+++ b/site/exports/jlu-math.xlsx
@@ -14,11 +14,11 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="来源" sheetId="5" state="visible" r:id="rId5"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'总览'!$A$1:$K$2</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'经历'!$A$1:$S$4</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'总览'!$A$1:$K$3</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'经历'!$A$1:$S$8</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'导师'!$A$1:$L$3</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">'论文'!$A$1:$L$3</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="4" hidden="1">'来源'!$A$1:$G$2</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">'论文'!$A$1:$L$5</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="4" hidden="1">'来源'!$A$1:$G$3</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -443,7 +443,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K2"/>
+  <dimension ref="A1:K3"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="16" customWidth="1" min="1" max="1"/>
@@ -453,8 +453,8 @@
     <col width="16" customWidth="1" min="5" max="5"/>
     <col width="65" customWidth="1" min="6" max="6"/>
     <col width="37.8" customWidth="1" min="7" max="7"/>
-    <col width="26.6" customWidth="1" min="8" max="8"/>
-    <col width="21" customWidth="1" min="9" max="9"/>
+    <col width="40.59999999999999" customWidth="1" min="8" max="8"/>
+    <col width="23.8" customWidth="1" min="9" max="9"/>
     <col width="16" customWidth="1" min="10" max="10"/>
     <col width="16" customWidth="1" min="11" max="11"/>
   </cols>
@@ -477,7 +477,7 @@
       </c>
       <c r="D1" s="1" t="inlineStr">
         <is>
-          <t>官方主页</t>
+          <t>个人主页／职业网站（来源类型见说明）</t>
         </is>
       </c>
       <c r="E1" s="1" t="inlineStr">
@@ -487,7 +487,7 @@
       </c>
       <c r="F1" s="1" t="inlineStr">
         <is>
-          <t>缺项与冲突</t>
+          <t>来源说明与待核事项</t>
         </is>
       </c>
       <c r="G1" s="1" t="inlineStr">
@@ -502,7 +502,7 @@
       </c>
       <c r="I1" s="1" t="inlineStr">
         <is>
-          <t>替代官方职业报道（非个人主页）</t>
+          <t>替代职业资料来源（非已核个人主页）</t>
         </is>
       </c>
       <c r="J1" s="1" t="inlineStr">
@@ -569,10 +569,64 @@
         </is>
       </c>
     </row>
+    <row r="3">
+      <c r="A3" s="2" t="inlineStr">
+        <is>
+          <t>王蕊</t>
+        </is>
+      </c>
+      <c r="B3" s="2" t="inlineStr">
+        <is>
+          <t>校区未标注</t>
+        </is>
+      </c>
+      <c r="C3" s="2" t="inlineStr">
+        <is>
+          <t>数学学院</t>
+        </is>
+      </c>
+      <c r="D3" s="3" t="inlineStr">
+        <is>
+          <t>https://math.jlu.edu.cn/info/1346/4542.htm</t>
+        </is>
+      </c>
+      <c r="E3" s="2" t="inlineStr">
+        <is>
+          <t>未知（来源日期异常）</t>
+        </is>
+      </c>
+      <c r="F3" s="2" t="inlineStr">
+        <is>
+          <t>Partial official biography only; independent directory and current employment unverified.；Necessary professional excerpts retained, not full original HTTP or complete page.；Degree labels or study episodes do not establish explicit conferral; unknown award status/dates remain unknown.；Selected bibliography only, publisher metadata and full text not verified.；来源差异/限制：Displayed publication date2017-11-30 (L79) coexists with retained2024 bibliographic entries; neither establishes last modification time.</t>
+        </is>
+      </c>
+      <c r="G3" s="2" t="inlineStr">
+        <is>
+          <t>分批核实资料，不是完整名录；人物整体核验日期未单独记录</t>
+        </is>
+      </c>
+      <c r="H3" s="2" t="inlineStr">
+        <is>
+          <t>官方资料（原来源）；公开个人页（访问与内容时效见来源记录）</t>
+        </is>
+      </c>
+      <c r="I3" s="2" t="inlineStr"/>
+      <c r="J3" s="2" t="inlineStr">
+        <is>
+          <t>jlu</t>
+        </is>
+      </c>
+      <c r="K3" s="2" t="inlineStr">
+        <is>
+          <t>吉林大学</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:K2"/>
+  <autoFilter ref="A1:K3"/>
   <hyperlinks>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D3" r:id="rId2"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -584,13 +638,13 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:S4"/>
+  <dimension ref="A1:S8"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="16" customWidth="1" min="1" max="1"/>
-    <col width="16.8" customWidth="1" min="2" max="2"/>
+    <col width="28" customWidth="1" min="2" max="2"/>
     <col width="16" customWidth="1" min="3" max="3"/>
-    <col width="16" customWidth="1" min="4" max="4"/>
+    <col width="25.2" customWidth="1" min="4" max="4"/>
     <col width="16" customWidth="1" min="5" max="5"/>
     <col width="16" customWidth="1" min="6" max="6"/>
     <col width="16" customWidth="1" min="7" max="7"/>
@@ -666,7 +720,7 @@
       </c>
       <c r="L1" s="1" t="inlineStr">
         <is>
-          <t>确证授位</t>
+          <t>来源记载学位</t>
         </is>
       </c>
       <c r="M1" s="1" t="inlineStr">
@@ -896,12 +950,278 @@
         </is>
       </c>
     </row>
+    <row r="5">
+      <c r="A5" s="2" t="inlineStr">
+        <is>
+          <t>王蕊</t>
+        </is>
+      </c>
+      <c r="B5" s="2" t="inlineStr">
+        <is>
+          <t>education_background</t>
+        </is>
+      </c>
+      <c r="C5" s="2" t="inlineStr">
+        <is>
+          <t>学士</t>
+        </is>
+      </c>
+      <c r="D5" s="2" t="inlineStr">
+        <is>
+          <t>北京师范大学数学系</t>
+        </is>
+      </c>
+      <c r="E5" s="2" t="inlineStr">
+        <is>
+          <t>1999-09</t>
+        </is>
+      </c>
+      <c r="F5" s="2" t="inlineStr">
+        <is>
+          <t>2003-07</t>
+        </is>
+      </c>
+      <c r="G5" s="2" t="inlineStr"/>
+      <c r="H5" s="2" t="inlineStr"/>
+      <c r="I5" s="2" t="inlineStr"/>
+      <c r="J5" s="2" t="inlineStr"/>
+      <c r="K5" s="2" t="inlineStr">
+        <is>
+          <t>unknown</t>
+        </is>
+      </c>
+      <c r="L5" s="2" t="inlineStr"/>
+      <c r="M5" s="2" t="inlineStr"/>
+      <c r="N5" s="2" t="inlineStr"/>
+      <c r="O5" s="2" t="inlineStr">
+        <is>
+          <t>本轮按留存来源记录整理；学位资格为来源记载，不代表独立证书认证。</t>
+        </is>
+      </c>
+      <c r="P5" s="2" t="inlineStr"/>
+      <c r="Q5" s="3" t="inlineStr">
+        <is>
+          <t>https://math.jlu.edu.cn/info/1346/4542.htm</t>
+        </is>
+      </c>
+      <c r="R5" s="2" t="inlineStr">
+        <is>
+          <t>jlu</t>
+        </is>
+      </c>
+      <c r="S5" s="2" t="inlineStr">
+        <is>
+          <t>吉林大学</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="2" t="inlineStr">
+        <is>
+          <t>王蕊</t>
+        </is>
+      </c>
+      <c r="B6" s="2" t="inlineStr">
+        <is>
+          <t>education_background</t>
+        </is>
+      </c>
+      <c r="C6" s="2" t="inlineStr">
+        <is>
+          <t>硕士</t>
+        </is>
+      </c>
+      <c r="D6" s="2" t="inlineStr">
+        <is>
+          <t>中国科学院数学与系统科学研究院</t>
+        </is>
+      </c>
+      <c r="E6" s="2" t="inlineStr">
+        <is>
+          <t>2003-09</t>
+        </is>
+      </c>
+      <c r="F6" s="2" t="inlineStr">
+        <is>
+          <t>2005-07</t>
+        </is>
+      </c>
+      <c r="G6" s="2" t="inlineStr"/>
+      <c r="H6" s="2" t="inlineStr"/>
+      <c r="I6" s="2" t="inlineStr"/>
+      <c r="J6" s="2" t="inlineStr"/>
+      <c r="K6" s="2" t="inlineStr">
+        <is>
+          <t>unknown</t>
+        </is>
+      </c>
+      <c r="L6" s="2" t="inlineStr"/>
+      <c r="M6" s="2" t="inlineStr"/>
+      <c r="N6" s="2" t="inlineStr"/>
+      <c r="O6" s="2" t="inlineStr">
+        <is>
+          <t>本轮按留存来源记录整理；学位资格为来源记载，不代表独立证书认证。</t>
+        </is>
+      </c>
+      <c r="P6" s="2" t="inlineStr"/>
+      <c r="Q6" s="3" t="inlineStr">
+        <is>
+          <t>https://math.jlu.edu.cn/info/1346/4542.htm</t>
+        </is>
+      </c>
+      <c r="R6" s="2" t="inlineStr">
+        <is>
+          <t>jlu</t>
+        </is>
+      </c>
+      <c r="S6" s="2" t="inlineStr">
+        <is>
+          <t>吉林大学</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="2" t="inlineStr">
+        <is>
+          <t>王蕊</t>
+        </is>
+      </c>
+      <c r="B7" s="2" t="inlineStr">
+        <is>
+          <t>education_background</t>
+        </is>
+      </c>
+      <c r="C7" s="2" t="inlineStr">
+        <is>
+          <t>博士</t>
+        </is>
+      </c>
+      <c r="D7" s="2" t="inlineStr">
+        <is>
+          <t>中国科学院数学与系统科学研究院</t>
+        </is>
+      </c>
+      <c r="E7" s="2" t="inlineStr">
+        <is>
+          <t>2005-09</t>
+        </is>
+      </c>
+      <c r="F7" s="2" t="inlineStr">
+        <is>
+          <t>2008-05</t>
+        </is>
+      </c>
+      <c r="G7" s="2" t="inlineStr"/>
+      <c r="H7" s="2" t="inlineStr"/>
+      <c r="I7" s="2" t="inlineStr"/>
+      <c r="J7" s="2" t="inlineStr"/>
+      <c r="K7" s="2" t="inlineStr">
+        <is>
+          <t>unknown</t>
+        </is>
+      </c>
+      <c r="L7" s="2" t="inlineStr"/>
+      <c r="M7" s="2" t="inlineStr"/>
+      <c r="N7" s="2" t="inlineStr"/>
+      <c r="O7" s="2" t="inlineStr">
+        <is>
+          <t>本轮按留存来源记录整理；学位资格为来源记载，不代表独立证书认证。</t>
+        </is>
+      </c>
+      <c r="P7" s="2" t="inlineStr"/>
+      <c r="Q7" s="3" t="inlineStr">
+        <is>
+          <t>https://math.jlu.edu.cn/info/1346/4542.htm</t>
+        </is>
+      </c>
+      <c r="R7" s="2" t="inlineStr">
+        <is>
+          <t>jlu</t>
+        </is>
+      </c>
+      <c r="S7" s="2" t="inlineStr">
+        <is>
+          <t>吉林大学</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="2" t="inlineStr">
+        <is>
+          <t>王蕊</t>
+        </is>
+      </c>
+      <c r="B8" s="2" t="inlineStr">
+        <is>
+          <t>education_background</t>
+        </is>
+      </c>
+      <c r="C8" s="2" t="inlineStr">
+        <is>
+          <t>博士后</t>
+        </is>
+      </c>
+      <c r="D8" s="2" t="inlineStr">
+        <is>
+          <t>中国科学院研究生院信息科学与工程学院</t>
+        </is>
+      </c>
+      <c r="E8" s="2" t="inlineStr">
+        <is>
+          <t>2008-05</t>
+        </is>
+      </c>
+      <c r="F8" s="2" t="inlineStr">
+        <is>
+          <t>2011-05</t>
+        </is>
+      </c>
+      <c r="G8" s="2" t="inlineStr"/>
+      <c r="H8" s="2" t="inlineStr"/>
+      <c r="I8" s="2" t="inlineStr"/>
+      <c r="J8" s="2" t="inlineStr"/>
+      <c r="K8" s="2" t="inlineStr">
+        <is>
+          <t>unknown</t>
+        </is>
+      </c>
+      <c r="L8" s="2" t="b">
+        <v>0</v>
+      </c>
+      <c r="M8" s="2" t="inlineStr"/>
+      <c r="N8" s="2" t="inlineStr"/>
+      <c r="O8" s="2" t="inlineStr">
+        <is>
+          <t>本轮按留存来源记录整理；学位资格为来源记载，不代表独立证书认证。</t>
+        </is>
+      </c>
+      <c r="P8" s="2" t="inlineStr"/>
+      <c r="Q8" s="3" t="inlineStr">
+        <is>
+          <t>https://math.jlu.edu.cn/info/1346/4542.htm</t>
+        </is>
+      </c>
+      <c r="R8" s="2" t="inlineStr">
+        <is>
+          <t>jlu</t>
+        </is>
+      </c>
+      <c r="S8" s="2" t="inlineStr">
+        <is>
+          <t>吉林大学</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:S4"/>
+  <autoFilter ref="A1:S8"/>
   <hyperlinks>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="Q2" r:id="rId1"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="Q3" r:id="rId2"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="Q4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="Q5" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="Q6" r:id="rId5"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="Q7" r:id="rId6"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="Q8" r:id="rId7"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -1100,7 +1420,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L3"/>
+  <dimension ref="A1:L5"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="16" customWidth="1" min="1" max="1"/>
@@ -1111,7 +1431,7 @@
     <col width="21" customWidth="1" min="6" max="6"/>
     <col width="58.8" customWidth="1" min="7" max="7"/>
     <col width="58.8" customWidth="1" min="8" max="8"/>
-    <col width="58.8" customWidth="1" min="9" max="9"/>
+    <col width="65" customWidth="1" min="9" max="9"/>
     <col width="65" customWidth="1" min="10" max="10"/>
     <col width="16" customWidth="1" min="11" max="11"/>
     <col width="16" customWidth="1" min="12" max="12"/>
@@ -1291,8 +1611,104 @@
         </is>
       </c>
     </row>
+    <row r="4">
+      <c r="A4" s="2" t="inlineStr">
+        <is>
+          <t>王蕊</t>
+        </is>
+      </c>
+      <c r="B4" s="2" t="inlineStr">
+        <is>
+          <t>A Duality Approach to Regularization Learning Problems in Banach Spaces</t>
+        </is>
+      </c>
+      <c r="C4" s="2" t="n">
+        <v>2024</v>
+      </c>
+      <c r="D4" s="2" t="inlineStr"/>
+      <c r="E4" s="3" t="inlineStr">
+        <is>
+          <t>https://math.jlu.edu.cn/info/1346/4542.htm</t>
+        </is>
+      </c>
+      <c r="F4" s="2" t="inlineStr"/>
+      <c r="G4" s="3" t="inlineStr">
+        <is>
+          <t>https://math.jlu.edu.cn/info/1346/4542.htm</t>
+        </is>
+      </c>
+      <c r="H4" s="2" t="inlineStr"/>
+      <c r="I4" s="2" t="inlineStr">
+        <is>
+          <t>留存来源记载；本轮未重新核验原网页、出版元数据或全文。；source_attributed_recovery_not_reverified</t>
+        </is>
+      </c>
+      <c r="J4" s="2" t="inlineStr">
+        <is>
+          <t>留存来源记载；本轮未重新核验原网页、出版元数据或全文。；来源authors_as_source：Raymond Cheng、Rui Wang、Yuesheng Xu；来源person_contribution_role_as_source：listed author；来源书目信息（卷）：81；来源书目信息（文章编号）：101818；来源书目信息（页码）：1-22</t>
+        </is>
+      </c>
+      <c r="K4" s="2" t="inlineStr">
+        <is>
+          <t>jlu</t>
+        </is>
+      </c>
+      <c r="L4" s="2" t="inlineStr">
+        <is>
+          <t>吉林大学</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="2" t="inlineStr">
+        <is>
+          <t>王蕊</t>
+        </is>
+      </c>
+      <c r="B5" s="2" t="inlineStr">
+        <is>
+          <t>Sparse Representer Theorems for Learning in Reproducing Kernel Banach Spaces</t>
+        </is>
+      </c>
+      <c r="C5" s="2" t="n">
+        <v>2024</v>
+      </c>
+      <c r="D5" s="2" t="inlineStr"/>
+      <c r="E5" s="3" t="inlineStr">
+        <is>
+          <t>https://math.jlu.edu.cn/info/1346/4542.htm</t>
+        </is>
+      </c>
+      <c r="F5" s="2" t="inlineStr"/>
+      <c r="G5" s="3" t="inlineStr">
+        <is>
+          <t>https://math.jlu.edu.cn/info/1346/4542.htm</t>
+        </is>
+      </c>
+      <c r="H5" s="2" t="inlineStr"/>
+      <c r="I5" s="2" t="inlineStr">
+        <is>
+          <t>留存来源记载；本轮未重新核验原网页、出版元数据或全文。；source_attributed_recovery_not_reverified</t>
+        </is>
+      </c>
+      <c r="J5" s="2" t="inlineStr">
+        <is>
+          <t>留存来源记载；本轮未重新核验原网页、出版元数据或全文。；来源authors_as_source：Rui Wang、Yuesheng Xu、Mingsong Yan；来源person_contribution_role_as_source：listed author；来源书目信息（卷）：25；来源书目信息（文章编号）：93；来源书目信息（页码）：1-45</t>
+        </is>
+      </c>
+      <c r="K5" s="2" t="inlineStr">
+        <is>
+          <t>jlu</t>
+        </is>
+      </c>
+      <c r="L5" s="2" t="inlineStr">
+        <is>
+          <t>吉林大学</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:L3"/>
+  <autoFilter ref="A1:L5"/>
   <hyperlinks>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E2" r:id="rId1"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G2" r:id="rId2"/>
@@ -1300,6 +1716,10 @@
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E3" r:id="rId4"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G3" r:id="rId5"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H3" r:id="rId6"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E4" r:id="rId7"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G4" r:id="rId8"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E5" r:id="rId9"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G5" r:id="rId10"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -1311,14 +1731,14 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G2"/>
+  <dimension ref="A1:G3"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="16" customWidth="1" min="1" max="1"/>
-    <col width="29.4" customWidth="1" min="2" max="2"/>
+    <col width="58.8" customWidth="1" min="2" max="2"/>
     <col width="58.8" customWidth="1" min="3" max="3"/>
-    <col width="16" customWidth="1" min="4" max="4"/>
-    <col width="16" customWidth="1" min="5" max="5"/>
+    <col width="65" customWidth="1" min="4" max="4"/>
+    <col width="28" customWidth="1" min="5" max="5"/>
     <col width="16" customWidth="1" min="6" max="6"/>
     <col width="16" customWidth="1" min="7" max="7"/>
   </cols>
@@ -1393,10 +1813,48 @@
         </is>
       </c>
     </row>
+    <row r="3">
+      <c r="A3" s="2" t="inlineStr">
+        <is>
+          <t>王蕊</t>
+        </is>
+      </c>
+      <c r="B3" s="2" t="inlineStr">
+        <is>
+          <t>new-recovery-jlu-wangrui-s001-8248a6a47655</t>
+        </is>
+      </c>
+      <c r="C3" s="3" t="inlineStr">
+        <is>
+          <t>https://math.jlu.edu.cn/info/1346/4542.htm</t>
+        </is>
+      </c>
+      <c r="D3" s="2" t="inlineStr">
+        <is>
+          <t>留存来源记录（本轮重新审查；非独立证书认证）；NEW_RECOVERY：依据留存来源摘录、摘要或结构化记录；除另有本轮证据说明外未重新读取原网页，不继承旧核验结论。</t>
+        </is>
+      </c>
+      <c r="E3" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-25T05:42:07Z</t>
+        </is>
+      </c>
+      <c r="F3" s="2" t="inlineStr">
+        <is>
+          <t>jlu</t>
+        </is>
+      </c>
+      <c r="G3" s="2" t="inlineStr">
+        <is>
+          <t>吉林大学</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:G2"/>
+  <autoFilter ref="A1:G3"/>
   <hyperlinks>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C3" r:id="rId2"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
